--- a/data/trans_dic/P19F$noche-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,65; 82,65</t>
+          <t>69,22; 82,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64,67; 81,03</t>
+          <t>65,15; 80,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>69,32; 80,15</t>
+          <t>70,4; 79,92</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,56; 81,56</t>
+          <t>68,22; 81,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,91; 80,45</t>
+          <t>67,12; 79,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,84; 79,44</t>
+          <t>70,38; 79,56</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72,46; 82,66</t>
+          <t>73,43; 82,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,62; 93,36</t>
+          <t>79,22; 94,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,74; 84,12</t>
+          <t>76,01; 83,82</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,35; 80,11</t>
+          <t>73,2; 80,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,9; 84,5</t>
+          <t>77,11; 84,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,84; 81,15</t>
+          <t>75,95; 81,37</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,78; 84,37</t>
+          <t>75,13; 84,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,44; 86,72</t>
+          <t>78,86; 86,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,42; 84,38</t>
+          <t>78,8; 84,58</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>72,37; 85,43</t>
+          <t>71,54; 85,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,07; 85,08</t>
+          <t>78,09; 85,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,93; 84,02</t>
+          <t>78,28; 84,04</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,64; 79,59</t>
+          <t>75,72; 79,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,75; 82,62</t>
+          <t>79,01; 82,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,84; 80,64</t>
+          <t>77,8; 80,57</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>139133; 165099</t>
+          <t>138272; 164575</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83317; 104392</t>
+          <t>83935; 103327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>227769; 263354</t>
+          <t>231316; 262614</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122838; 146126</t>
+          <t>122229; 146584</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120074; 144376</t>
+          <t>120459; 143554</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>250455; 284880</t>
+          <t>252386; 285310</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>204402; 233181</t>
+          <t>207132; 234011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57881; 69614</t>
+          <t>59068; 70281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>270112; 300031</t>
+          <t>271106; 298959</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>456722; 498804</t>
+          <t>455805; 498674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>325037; 357184</t>
+          <t>325934; 356665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>792869; 848322</t>
+          <t>793960; 850631</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>255383; 284361</t>
+          <t>253198; 283228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>321633; 351111</t>
+          <t>319265; 350661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>581800; 625976</t>
+          <t>584638; 627505</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>113570; 134076</t>
+          <t>112268; 133813</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>411977; 448943</t>
+          <t>412071; 448893</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533544; 575204</t>
+          <t>535955; 575336</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1344536; 1414871</t>
+          <t>1346041; 1418057</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1368820; 1435967</t>
+          <t>1373333; 1436181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2736572; 2835057</t>
+          <t>2735160; 2832589</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$noche-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,22; 82,39</t>
+          <t>70,26; 82,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,15; 80,2</t>
+          <t>65,04; 80,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,4; 79,92</t>
+          <t>69,99; 79,99</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,22; 81,82</t>
+          <t>68,51; 81,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,12; 79,99</t>
+          <t>66,84; 81,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,38; 79,56</t>
+          <t>69,52; 79,35</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,43; 82,96</t>
+          <t>73,61; 83,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,22; 94,25</t>
+          <t>77,11; 93,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76,01; 83,82</t>
+          <t>75,63; 84,04</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,2; 80,08</t>
+          <t>73,24; 80,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,11; 84,38</t>
+          <t>76,72; 84,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,95; 81,37</t>
+          <t>75,73; 80,9</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,13; 84,04</t>
+          <t>75,49; 84,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,86; 86,61</t>
+          <t>79,36; 87,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,8; 84,58</t>
+          <t>78,61; 84,57</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,54; 85,27</t>
+          <t>72,09; 85,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78,09; 85,07</t>
+          <t>78,23; 85,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,28; 84,04</t>
+          <t>78,02; 84,25</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,72; 79,77</t>
+          <t>75,67; 79,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79,01; 82,63</t>
+          <t>78,92; 82,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,8; 80,57</t>
+          <t>77,82; 80,64</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>138272; 164575</t>
+          <t>140357; 164160</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83935; 103327</t>
+          <t>83793; 104047</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>231316; 262614</t>
+          <t>229997; 262826</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122229; 146584</t>
+          <t>122745; 146790</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>120459; 143554</t>
+          <t>119954; 145536</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>252386; 285310</t>
+          <t>249325; 284562</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>207132; 234011</t>
+          <t>207637; 235171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59068; 70281</t>
+          <t>57496; 69580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>271106; 298959</t>
+          <t>269738; 299732</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>455805; 498674</t>
+          <t>456030; 499639</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>325934; 356665</t>
+          <t>324290; 356045</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>793960; 850631</t>
+          <t>791674; 845714</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>253198; 283228</t>
+          <t>254412; 283425</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>319265; 350661</t>
+          <t>321312; 352407</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>584638; 627505</t>
+          <t>583216; 627406</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>112268; 133813</t>
+          <t>113131; 133462</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>412071; 448893</t>
+          <t>412809; 449872</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>535955; 575336</t>
+          <t>534169; 576797</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1346041; 1418057</t>
+          <t>1345232; 1417642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1373333; 1436181</t>
+          <t>1371645; 1438387</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2735160; 2832589</t>
+          <t>2736150; 2835286</t>
         </is>
       </c>
     </row>
